--- a/backend/data/financials_by_company/0237.HK.xlsx
+++ b/backend/data/financials_by_company/0237.HK.xlsx
@@ -2966,187 +2966,187 @@
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
       <c r="DE1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EN1" t="inlineStr">
@@ -3252,25 +3252,25 @@
         <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="W2" t="n">
         <v>2.2</v>
       </c>
       <c r="X2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Y2" t="n">
         <v>2.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AA2" t="n">
         <v>2.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC2" t="n">
         <v>0.08</v>
@@ -3288,16 +3288,16 @@
         <v>3.45</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.192</v>
+        <v>0.186</v>
       </c>
       <c r="AI2" t="n">
-        <v>46000</v>
+        <v>4000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>46000</v>
+        <v>4000</v>
       </c>
       <c r="AK2" t="n">
-        <v>22880</v>
+        <v>22713</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -3306,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AO2" t="n">
         <v>2.2</v>
@@ -3321,7 +3321,7 @@
         <v>891000000</v>
       </c>
       <c r="AS2" t="n">
-        <v>891000000</v>
+        <v>895050000</v>
       </c>
       <c r="AT2" t="n">
         <v>1.82</v>
@@ -3339,10 +3339,10 @@
         <v>3.790941</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.2218</v>
+        <v>2.2266</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.10465</v>
+        <v>2.1048</v>
       </c>
       <c r="BA2" t="n">
         <v>0.08</v>
@@ -3415,10 +3415,10 @@
         <v>2.427</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.20218575</v>
+        <v>0.18279564</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27294624</v>
+        <v>0.22635591</v>
       </c>
       <c r="BY2" t="n">
         <v>0.03</v>
@@ -3530,138 +3530,138 @@
       </c>
       <c r="DC2" t="inlineStr">
         <is>
+          <t>Safety Godown Company, Limited</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
           <t>SAFETY GODOWN</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Safety Godown Company, Limited</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DF2" t="n">
-        <v>1780280826</v>
-      </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DI2" t="n">
+        <v>1780884741</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>finmb_7654855</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DK2" t="n">
+      <c r="DN2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DM2" t="b">
+      <c r="DP2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="b">
+      <c r="DQ2" t="n">
+        <v>-0.026599884</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.011946414</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.09520006</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.04522998</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DW2" t="b">
         <v>0</v>
       </c>
-      <c r="DO2" t="n">
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
         <v>947640600000</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DZ2" t="n">
         <v>0</v>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>2.2 - 2.21</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>2.2 - 2.2</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DS2" t="n">
-        <v>22880</v>
-      </c>
-      <c r="DT2" t="n">
+      <c r="EC2" t="n">
+        <v>22713</v>
+      </c>
+      <c r="ED2" t="n">
         <v>0.38</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="EE2" t="n">
         <v>0.2087912</v>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>1.82 - 2.45</t>
         </is>
       </c>
-      <c r="DW2" t="n">
+      <c r="EG2" t="n">
         <v>-0.25</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EH2" t="n">
         <v>-0.10204081</v>
       </c>
-      <c r="DY2" t="n">
-        <v>20.218575</v>
-      </c>
-      <c r="DZ2" t="n">
+      <c r="EI2" t="n">
+        <v>18.279564</v>
+      </c>
+      <c r="EJ2" t="n">
         <v>1732788675</v>
       </c>
-      <c r="EA2" t="n">
+      <c r="EK2" t="n">
         <v>1732788675</v>
       </c>
-      <c r="EB2" t="b">
+      <c r="EL2" t="b">
         <v>0</v>
       </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="EF2" t="n">
+      <c r="EM2" t="n">
         <v>-0.7</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.021800041</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.009811883</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.09535003</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.04530446</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EM2" t="b">
-        <v>0</v>
       </c>
       <c r="EN2" t="inlineStr"/>
     </row>
